--- a/artfynd/A 4544-2024 artfynd.xlsx
+++ b/artfynd/A 4544-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4544-2024 artfynd.xlsx
+++ b/artfynd/A 4544-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91836474</v>
+        <v>91836471</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630236.1968598688</v>
+        <v>630306</v>
       </c>
       <c r="R2" t="n">
-        <v>7306326.947675626</v>
+        <v>7306201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91836479</v>
+        <v>91836472</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630277.8977874607</v>
+        <v>630454</v>
       </c>
       <c r="R3" t="n">
-        <v>7306357.963823188</v>
+        <v>7306285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91836464</v>
+        <v>91836474</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630470.8718754409</v>
+        <v>630236</v>
       </c>
       <c r="R4" t="n">
-        <v>7306276.931580307</v>
+        <v>7306327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91836472</v>
+        <v>91836475</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630454.0715628834</v>
+        <v>630489</v>
       </c>
       <c r="R5" t="n">
-        <v>7306285.189156123</v>
+        <v>7306269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91836465</v>
+        <v>91836486</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630289.1656451272</v>
+        <v>630404</v>
       </c>
       <c r="R6" t="n">
-        <v>7306372.010652033</v>
+        <v>7306319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91836471</v>
+        <v>91836463</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630305.9840806866</v>
+        <v>630199</v>
       </c>
       <c r="R7" t="n">
-        <v>7306200.929043682</v>
+        <v>7306233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91836457</v>
+        <v>91836458</v>
       </c>
       <c r="B8" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630238.0594136035</v>
+        <v>630236</v>
       </c>
       <c r="R8" t="n">
-        <v>7306331.133685526</v>
+        <v>7306327</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91836456</v>
+        <v>91836478</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630258.955878331</v>
+        <v>630459</v>
       </c>
       <c r="R9" t="n">
-        <v>7306295.992696041</v>
+        <v>7306294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91836470</v>
+        <v>91836479</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630328.8170510551</v>
+        <v>630278</v>
       </c>
       <c r="R10" t="n">
-        <v>7306375.865877837</v>
+        <v>7306358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91836459</v>
+        <v>91836487</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630271.8999262226</v>
+        <v>630294</v>
       </c>
       <c r="R11" t="n">
-        <v>7306264.180809967</v>
+        <v>7306210</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91836461</v>
+        <v>91836477</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630411.1581557312</v>
+        <v>630242</v>
       </c>
       <c r="R12" t="n">
-        <v>7306316.865430531</v>
+        <v>7306331</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91836480</v>
+        <v>91836457</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630402.9825549963</v>
+        <v>630238</v>
       </c>
       <c r="R13" t="n">
-        <v>7306298.037021833</v>
+        <v>7306331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91836458</v>
+        <v>91836459</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630236.1968598688</v>
+        <v>630272</v>
       </c>
       <c r="R14" t="n">
-        <v>7306326.947675626</v>
+        <v>7306264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91836486</v>
+        <v>91836464</v>
       </c>
       <c r="B15" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630404.08063377</v>
+        <v>630471</v>
       </c>
       <c r="R15" t="n">
-        <v>7306319.003881599</v>
+        <v>7306277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91836487</v>
+        <v>91836465</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630294.0823707648</v>
+        <v>630289</v>
       </c>
       <c r="R16" t="n">
-        <v>7306209.820843006</v>
+        <v>7306372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>91836477</v>
+        <v>91836470</v>
       </c>
       <c r="B17" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630242.175466411</v>
+        <v>630329</v>
       </c>
       <c r="R17" t="n">
-        <v>7306330.910783453</v>
+        <v>7306376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,6 +2224,103 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>91836488</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Gaika, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630456</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7306242</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-07-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-07-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4544-2024 artfynd.xlsx
+++ b/artfynd/A 4544-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836471</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836472</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836474</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836475</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836486</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836463</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836458</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836478</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836479</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836487</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836477</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836457</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836459</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836464</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836465</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836470</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,8 +2406,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91836488</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>